--- a/histograms/histogram_CatW__g_L.xlsx
+++ b/histograms/histogram_CatW__g_L.xlsx
@@ -442,79 +442,79 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.25324675</v>
+        <v>0.2824675</v>
       </c>
       <c r="B2" t="n">
-        <v>22256</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3.75308025</v>
+        <v>0.7808025000000001</v>
       </c>
       <c r="B3" t="n">
-        <v>2776</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>6.252913750000001</v>
+        <v>1.2791375</v>
       </c>
       <c r="B4" t="n">
-        <v>619</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8.752747250000001</v>
+        <v>1.7774725</v>
       </c>
       <c r="B5" t="n">
-        <v>502</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>11.25258075</v>
+        <v>2.2758075</v>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>13.75241425</v>
+        <v>2.7741425</v>
       </c>
       <c r="B7" t="n">
-        <v>210</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16.25224775</v>
+        <v>3.2724775</v>
       </c>
       <c r="B8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18.75208125</v>
+        <v>3.7708125</v>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>21.25191475</v>
+        <v>4.269147499999999</v>
       </c>
       <c r="B10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>23.75174825</v>
+        <v>4.7674825</v>
       </c>
       <c r="B11" t="n">
         <v>1</v>
@@ -522,7 +522,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>26.25158175</v>
+        <v>5.265817499999999</v>
       </c>
       <c r="B12" t="n">
         <v>0</v>
@@ -530,15 +530,15 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>28.75141525</v>
+        <v>5.7641525</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31.25124875</v>
+        <v>6.262487499999999</v>
       </c>
       <c r="B14" t="n">
         <v>0</v>
@@ -546,15 +546,15 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>33.75108225</v>
+        <v>6.7608225</v>
       </c>
       <c r="B15" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>36.25091575</v>
+        <v>7.259157499999999</v>
       </c>
       <c r="B16" t="n">
         <v>0</v>
@@ -562,7 +562,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>38.75074925</v>
+        <v>7.7574925</v>
       </c>
       <c r="B17" t="n">
         <v>0</v>
@@ -570,7 +570,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>41.25058275000001</v>
+        <v>8.255827500000001</v>
       </c>
       <c r="B18" t="n">
         <v>0</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>43.75041625</v>
+        <v>8.7541625</v>
       </c>
       <c r="B19" t="n">
         <v>0</v>
@@ -586,7 +586,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.25024975000001</v>
+        <v>9.2524975</v>
       </c>
       <c r="B20" t="n">
         <v>0</v>
@@ -594,10 +594,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>48.75008325</v>
+        <v>9.7508325</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
